--- a/output/2026-09-06_20_Slovenia_Osrednjeslovenska_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-06_20_Slovenia_Osrednjeslovenska_Depolverazione_Trattamento_aria.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rappresentante ufficiale confermato di ULT AG (Germania) per aspirazione industriale, filtrazione e climatizzazione aria di processo. Verificato via WebSearch.</t>
+          <t>Rappresentante ufficiale confermato di ULT AG (Germania) per aspirazione industriale, filtrazione e climatizzazione aria di processo. Verificato via WebSearch. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,11 +573,9 @@
           <t>Depolverazione / Trattamento aria</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fornitore/system-integrator confermato di soluzioni di ventilazione, filtrazione industriale e sistemi multistadio di depolverazione. Telefono/email non reperiti. Verificato via WebSearch.</t>
+          <t>Fornitore/system-integrator confermato di soluzioni di ventilazione, filtrazione industriale e sistemi multistadio di depolverazione. Telefono/email non reperiti. Verificato via WebSearch. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -661,7 +659,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Confermato rappresentante ufficiale Nederman (Svezia) per la Slovenia: aspirazione fumi di saldatura, polveri, sistemi di filtrazione fissi e mobili, ricambi e assistenza. Verificato via WebSearch.</t>
+          <t>Confermato rappresentante ufficiale Nederman (Svezia) per la Slovenia: aspirazione fumi di saldatura, polveri, sistemi di filtrazione fissi e mobili, ricambi e assistenza. Verificato via WebSearch. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -703,7 +701,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Confermato produttore/distributore storico (dal 1990) di filtri industriali; rappresenta Donaldson Torit e TEKA per depolverazione e nebbia oleosa. Verificato via WebSearch.</t>
+          <t>Confermato produttore/distributore storico (dal 1990) di filtri industriali; rappresenta Donaldson Torit e TEKA per depolverazione e nebbia oleosa. Verificato via WebSearch. [DUPLICATO — vedi anche: 2026-09-06_01_Slovenia_Podravska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
